--- a/products-storage/00-free-ks-bez-vozvrata/02-reestr-prilozheniy.xlsx
+++ b/products-storage/00-free-ks-bez-vozvrata/02-reestr-prilozheniy.xlsx
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="E7" s="2">
-        <f>SUM(E2:E20)</f>
+        <f>SUM(E2:E6)</f>
         <v/>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
